--- a/excel/butterScaler/butterScaler23-Section06.xlsx
+++ b/excel/butterScaler/butterScaler23-Section06.xlsx
@@ -1,27 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10317"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10331"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shimin/Desktop/Shimin/4-Hobby/Hileft/CreatingMoviesUsingMusicAndScripts/excel/butterScaler/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4B4348D-24F3-E449-BF18-711F364CCFE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E883FE1-C07F-244F-82F7-6B97125A9F48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-12200" yWindow="-28200" windowWidth="34400" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="820" yWindow="-22560" windowWidth="30240" windowHeight="18120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="143">
   <si>
     <t>ActionName</t>
   </si>
@@ -170,9 +169,6 @@
     <t>旋转45度下蹲</t>
   </si>
   <si>
-    <t>身体旋转45度蹲(组合)</t>
-  </si>
-  <si>
     <t>碎步跑+旋转45度组合</t>
   </si>
   <si>
@@ -281,9 +277,6 @@
     <t>4,  3,  2,  1</t>
   </si>
   <si>
-    <t>先做深蹲</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Come on Go</t>
   </si>
   <si>
@@ -377,9 +370,6 @@
     <t>（碎步跑）go</t>
   </si>
   <si>
-    <t>跳跃转体</t>
-  </si>
-  <si>
     <t>（碎步跑）wow</t>
   </si>
   <si>
@@ -395,9 +385,6 @@
     <t>换脚，预先提示</t>
   </si>
   <si>
-    <t xml:space="preserve">先做深蹲,  </t>
-  </si>
-  <si>
     <t>Come on Go</t>
   </si>
   <si>
@@ -450,6 +437,18 @@
   </si>
   <si>
     <t>跳跃要来咯</t>
+  </si>
+  <si>
+    <t>碎步跑+身体旋转45度蹲</t>
+  </si>
+  <si>
+    <t>碎步跑+跳跃转体</t>
+  </si>
+  <si>
+    <t>先做深蹲，弓步蹲从右脚开始</t>
+  </si>
+  <si>
+    <t>先做深蹲,  弓步蹲从左脚开始</t>
   </si>
 </sst>
 </file>
@@ -869,7 +868,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
@@ -932,10 +931,13 @@
         <v>15</v>
       </c>
       <c r="E5" t="s">
-        <v>86</v>
+        <v>141</v>
       </c>
       <c r="F5" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G5" t="s">
+        <v>16</v>
       </c>
       <c r="H5" t="b">
         <v>0</v>
@@ -952,7 +954,7 @@
         <v>4</v>
       </c>
       <c r="D6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E6" t="s">
         <v>17</v>
@@ -961,7 +963,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
@@ -975,7 +977,7 @@
         <v>4</v>
       </c>
       <c r="D7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E7" t="s">
         <v>18</v>
@@ -1024,7 +1026,7 @@
         <v>21</v>
       </c>
       <c r="E9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
@@ -1047,7 +1049,7 @@
         <v>4</v>
       </c>
       <c r="D10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E10" t="s">
         <v>23</v>
@@ -1056,7 +1058,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
@@ -1073,7 +1075,7 @@
         <v>24</v>
       </c>
       <c r="E11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F11" t="b">
         <v>0</v>
@@ -1096,7 +1098,7 @@
         <v>25</v>
       </c>
       <c r="E12" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F12" t="b">
         <v>0</v>
@@ -1165,7 +1167,7 @@
         <v>24</v>
       </c>
       <c r="E15" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F15" t="b">
         <v>0</v>
@@ -1188,7 +1190,7 @@
         <v>29</v>
       </c>
       <c r="E16" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F16" t="b">
         <v>0</v>
@@ -1211,7 +1213,7 @@
         <v>24</v>
       </c>
       <c r="E17" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
@@ -1234,16 +1236,16 @@
         <v>4</v>
       </c>
       <c r="D18" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E18" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F18" t="b">
         <v>0</v>
       </c>
       <c r="H18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
@@ -1257,7 +1259,7 @@
         <v>4</v>
       </c>
       <c r="D19" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E19" t="s">
         <v>31</v>
@@ -1280,7 +1282,7 @@
         <v>4</v>
       </c>
       <c r="D20" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E20" t="s">
         <v>32</v>
@@ -1303,10 +1305,10 @@
         <v>4</v>
       </c>
       <c r="D21" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E21" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F21" t="b">
         <v>1</v>
@@ -1332,13 +1334,13 @@
         <v>34</v>
       </c>
       <c r="E22" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F22" t="b">
         <v>0</v>
       </c>
       <c r="H22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
@@ -1352,7 +1354,7 @@
         <v>4</v>
       </c>
       <c r="D23" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E23" t="s">
         <v>35</v>
@@ -1395,10 +1397,10 @@
         <v>4</v>
       </c>
       <c r="D25" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E25" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F25" t="b">
         <v>1</v>
@@ -1421,16 +1423,16 @@
         <v>4</v>
       </c>
       <c r="D26" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E26" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F26" t="b">
         <v>0</v>
       </c>
       <c r="H26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
@@ -1444,7 +1446,7 @@
         <v>4</v>
       </c>
       <c r="D27" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E27" t="s">
         <v>39</v>
@@ -1467,10 +1469,10 @@
         <v>4</v>
       </c>
       <c r="D28" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E28" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F28" t="b">
         <v>0</v>
@@ -1490,7 +1492,7 @@
         <v>4</v>
       </c>
       <c r="E29" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F29" t="b">
         <v>1</v>
@@ -1513,7 +1515,7 @@
         <v>4</v>
       </c>
       <c r="D30" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E30" t="s">
         <v>41</v>
@@ -1522,7 +1524,7 @@
         <v>0</v>
       </c>
       <c r="H30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
@@ -1536,7 +1538,7 @@
         <v>4</v>
       </c>
       <c r="D31" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E31" t="s">
         <v>42</v>
@@ -1559,10 +1561,10 @@
         <v>4</v>
       </c>
       <c r="D32" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E32" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F32" t="b">
         <v>0</v>
@@ -1585,7 +1587,7 @@
         <v>43</v>
       </c>
       <c r="E33" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F33" t="b">
         <v>1</v>
@@ -1614,7 +1616,7 @@
         <v>0</v>
       </c>
       <c r="H34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
@@ -1651,7 +1653,7 @@
         <v>47</v>
       </c>
       <c r="E36" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F36" t="b">
         <v>0</v>
@@ -1677,7 +1679,7 @@
         <v>1</v>
       </c>
       <c r="G37" t="s">
-        <v>49</v>
+        <v>139</v>
       </c>
       <c r="H37" t="b">
         <v>0</v>
@@ -1685,7 +1687,7 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B38">
         <v>8</v>
@@ -1694,21 +1696,21 @@
         <v>4</v>
       </c>
       <c r="D38" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E38" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F38" t="b">
         <v>0</v>
       </c>
       <c r="H38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B39">
         <v>8</v>
@@ -1717,10 +1719,10 @@
         <v>4</v>
       </c>
       <c r="D39" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E39" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F39" t="b">
         <v>0</v>
@@ -1731,7 +1733,7 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B40">
         <v>8</v>
@@ -1740,10 +1742,10 @@
         <v>4</v>
       </c>
       <c r="D40" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E40" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F40" t="b">
         <v>0</v>
@@ -1754,7 +1756,7 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B41">
         <v>8</v>
@@ -1763,10 +1765,10 @@
         <v>4</v>
       </c>
       <c r="D41" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E41" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F41" t="b">
         <v>0</v>
@@ -1777,7 +1779,7 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B42">
         <v>8</v>
@@ -1786,10 +1788,10 @@
         <v>4</v>
       </c>
       <c r="D42" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F42" t="b">
         <v>0</v>
@@ -1800,7 +1802,7 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B43">
         <v>8</v>
@@ -1809,10 +1811,10 @@
         <v>4</v>
       </c>
       <c r="D43" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E43" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F43" t="b">
         <v>0</v>
@@ -1823,7 +1825,7 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B44">
         <v>8</v>
@@ -1832,10 +1834,10 @@
         <v>4</v>
       </c>
       <c r="D44" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E44" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F44" t="b">
         <v>0</v>
@@ -1846,7 +1848,7 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B45">
         <v>8</v>
@@ -1855,16 +1857,16 @@
         <v>4</v>
       </c>
       <c r="D45" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E45" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F45" t="b">
         <v>1</v>
       </c>
       <c r="G45" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="H45" t="b">
         <v>0</v>
@@ -1872,7 +1874,7 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B46">
         <v>8</v>
@@ -1881,21 +1883,21 @@
         <v>4</v>
       </c>
       <c r="D46" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E46" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F46" t="b">
         <v>0</v>
       </c>
       <c r="H46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B47">
         <v>8</v>
@@ -1904,10 +1906,10 @@
         <v>4</v>
       </c>
       <c r="D47" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E47" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F47" t="b">
         <v>0</v>
@@ -1918,7 +1920,7 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B48">
         <v>8</v>
@@ -1927,10 +1929,10 @@
         <v>4</v>
       </c>
       <c r="D48" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E48" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F48" t="b">
         <v>0</v>
@@ -1941,19 +1943,19 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
+        <v>60</v>
+      </c>
+      <c r="B49">
+        <v>8</v>
+      </c>
+      <c r="C49">
+        <v>4</v>
+      </c>
+      <c r="D49" t="s">
+        <v>114</v>
+      </c>
+      <c r="E49" t="s">
         <v>61</v>
-      </c>
-      <c r="B49">
-        <v>8</v>
-      </c>
-      <c r="C49">
-        <v>4</v>
-      </c>
-      <c r="D49" t="s">
-        <v>116</v>
-      </c>
-      <c r="E49" t="s">
-        <v>62</v>
       </c>
       <c r="F49" t="b">
         <v>0</v>
@@ -1964,7 +1966,7 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B50">
         <v>8</v>
@@ -1973,21 +1975,21 @@
         <v>4</v>
       </c>
       <c r="D50" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E50" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F50" t="b">
         <v>0</v>
       </c>
       <c r="H50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B51">
         <v>8</v>
@@ -1996,7 +1998,7 @@
         <v>4</v>
       </c>
       <c r="D51" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F51" t="b">
         <v>0</v>
@@ -2007,7 +2009,7 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B52">
         <v>8</v>
@@ -2016,7 +2018,7 @@
         <v>4</v>
       </c>
       <c r="D52" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F52" t="b">
         <v>0</v>
@@ -2027,7 +2029,7 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B53">
         <v>8</v>
@@ -2036,13 +2038,13 @@
         <v>4</v>
       </c>
       <c r="D53" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F53" t="b">
         <v>1</v>
       </c>
       <c r="G53" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H53" t="b">
         <v>0</v>
@@ -2068,7 +2070,7 @@
         <v>0</v>
       </c>
       <c r="H54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.2">
@@ -2131,10 +2133,13 @@
         <v>15</v>
       </c>
       <c r="E57" t="s">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="F57" t="b">
         <v>0</v>
+      </c>
+      <c r="G57" t="s">
+        <v>16</v>
       </c>
       <c r="H57" t="b">
         <v>0</v>
@@ -2151,16 +2156,16 @@
         <v>4</v>
       </c>
       <c r="D58" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="E58" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F58" t="b">
         <v>0</v>
       </c>
       <c r="H58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.2">
@@ -2174,10 +2179,10 @@
         <v>4</v>
       </c>
       <c r="D59" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E59" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F59" t="b">
         <v>0</v>
@@ -2223,7 +2228,7 @@
         <v>21</v>
       </c>
       <c r="E61" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F61" t="b">
         <v>1</v>
@@ -2246,16 +2251,16 @@
         <v>4</v>
       </c>
       <c r="D62" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="E62" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F62" t="b">
         <v>0</v>
       </c>
       <c r="H62" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.2">
@@ -2272,7 +2277,7 @@
         <v>24</v>
       </c>
       <c r="E63" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F63" t="b">
         <v>0</v>
@@ -2295,7 +2300,7 @@
         <v>25</v>
       </c>
       <c r="E64" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F64" t="b">
         <v>0</v>
@@ -2384,7 +2389,7 @@
         <v>29</v>
       </c>
       <c r="E68" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F68" t="b">
         <v>0</v>
@@ -2407,7 +2412,7 @@
         <v>24</v>
       </c>
       <c r="E69" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="F69" t="b">
         <v>1</v>
@@ -2430,16 +2435,16 @@
         <v>4</v>
       </c>
       <c r="D70" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E70" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="F70" t="b">
         <v>0</v>
       </c>
       <c r="H70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.2">
@@ -2453,10 +2458,10 @@
         <v>4</v>
       </c>
       <c r="D71" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E71" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F71" t="b">
         <v>0</v>
@@ -2476,7 +2481,7 @@
         <v>4</v>
       </c>
       <c r="D72" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E72" t="s">
         <v>32</v>
@@ -2502,7 +2507,7 @@
         <v>33</v>
       </c>
       <c r="E73" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="F73" t="b">
         <v>1</v>
@@ -2525,16 +2530,16 @@
         <v>4</v>
       </c>
       <c r="D74" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E74" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F74" t="b">
         <v>0</v>
       </c>
       <c r="H74" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.2">
@@ -2588,7 +2593,7 @@
         <v>4</v>
       </c>
       <c r="D77" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E77" t="s">
         <v>37</v>
@@ -2614,16 +2619,16 @@
         <v>4</v>
       </c>
       <c r="D78" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E78" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="F78" t="b">
         <v>0</v>
       </c>
       <c r="H78" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.2">
@@ -2637,7 +2642,7 @@
         <v>4</v>
       </c>
       <c r="D79" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E79" t="s">
         <v>39</v>
@@ -2660,10 +2665,10 @@
         <v>4</v>
       </c>
       <c r="D80" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E80" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F80" t="b">
         <v>0</v>
@@ -2683,10 +2688,10 @@
         <v>4</v>
       </c>
       <c r="D81" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E81" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="F81" t="b">
         <v>1</v>
@@ -2709,7 +2714,7 @@
         <v>4</v>
       </c>
       <c r="D82" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="E82" t="s">
         <v>41</v>
@@ -2718,7 +2723,7 @@
         <v>0</v>
       </c>
       <c r="H82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.2">
@@ -2732,7 +2737,7 @@
         <v>4</v>
       </c>
       <c r="D83" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E83" t="s">
         <v>42</v>
@@ -2755,10 +2760,10 @@
         <v>4</v>
       </c>
       <c r="D84" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E84" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F84" t="b">
         <v>0</v>
@@ -2781,7 +2786,7 @@
         <v>43</v>
       </c>
       <c r="E85" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F85" t="b">
         <v>1</v>
@@ -2810,7 +2815,7 @@
         <v>0</v>
       </c>
       <c r="H86" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.2">
@@ -2847,7 +2852,7 @@
         <v>47</v>
       </c>
       <c r="E88" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F88" t="b">
         <v>0</v>
@@ -2873,7 +2878,7 @@
         <v>1</v>
       </c>
       <c r="G89" t="s">
-        <v>49</v>
+        <v>139</v>
       </c>
       <c r="H89" t="b">
         <v>0</v>
@@ -2881,30 +2886,30 @@
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
+        <v>49</v>
+      </c>
+      <c r="B90">
+        <v>8</v>
+      </c>
+      <c r="C90">
+        <v>4</v>
+      </c>
+      <c r="D90" t="s">
         <v>50</v>
       </c>
-      <c r="B90">
-        <v>8</v>
-      </c>
-      <c r="C90">
-        <v>4</v>
-      </c>
-      <c r="D90" t="s">
-        <v>51</v>
-      </c>
       <c r="E90" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F90" t="b">
         <v>0</v>
       </c>
       <c r="H90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B91">
         <v>8</v>
@@ -2913,10 +2918,10 @@
         <v>4</v>
       </c>
       <c r="D91" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E91" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F91" t="b">
         <v>0</v>
@@ -2927,7 +2932,7 @@
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B92">
         <v>8</v>
@@ -2936,10 +2941,10 @@
         <v>4</v>
       </c>
       <c r="D92" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E92" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F92" t="b">
         <v>0</v>
@@ -2950,7 +2955,7 @@
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B93">
         <v>8</v>
@@ -2959,10 +2964,10 @@
         <v>4</v>
       </c>
       <c r="D93" t="s">
+        <v>53</v>
+      </c>
+      <c r="E93" t="s">
         <v>54</v>
-      </c>
-      <c r="E93" t="s">
-        <v>55</v>
       </c>
       <c r="F93" t="b">
         <v>0</v>
@@ -2973,7 +2978,7 @@
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B94">
         <v>8</v>
@@ -2982,10 +2987,10 @@
         <v>4</v>
       </c>
       <c r="D94" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E94" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F94" t="b">
         <v>0</v>
@@ -2996,7 +3001,7 @@
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B95">
         <v>8</v>
@@ -3005,10 +3010,10 @@
         <v>4</v>
       </c>
       <c r="D95" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E95" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F95" t="b">
         <v>0</v>
@@ -3019,7 +3024,7 @@
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B96">
         <v>8</v>
@@ -3028,10 +3033,10 @@
         <v>4</v>
       </c>
       <c r="D96" t="s">
+        <v>57</v>
+      </c>
+      <c r="E96" t="s">
         <v>58</v>
-      </c>
-      <c r="E96" t="s">
-        <v>59</v>
       </c>
       <c r="F96" t="b">
         <v>0</v>
@@ -3042,7 +3047,7 @@
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B97">
         <v>8</v>
@@ -3051,16 +3056,16 @@
         <v>4</v>
       </c>
       <c r="D97" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E97" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="F97" t="b">
         <v>1</v>
       </c>
       <c r="G97" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="H97" t="b">
         <v>0</v>
@@ -3068,7 +3073,7 @@
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B98">
         <v>8</v>
@@ -3077,18 +3082,18 @@
         <v>4</v>
       </c>
       <c r="D98" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F98" t="b">
         <v>0</v>
       </c>
       <c r="H98" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B99">
         <v>8</v>
@@ -3097,10 +3102,10 @@
         <v>4</v>
       </c>
       <c r="D99" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E99" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F99" t="b">
         <v>0</v>
@@ -3111,7 +3116,7 @@
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B100">
         <v>8</v>
@@ -3120,10 +3125,10 @@
         <v>4</v>
       </c>
       <c r="D100" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E100" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F100" t="b">
         <v>0</v>
@@ -3134,19 +3139,19 @@
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
+        <v>60</v>
+      </c>
+      <c r="B101">
+        <v>8</v>
+      </c>
+      <c r="C101">
+        <v>4</v>
+      </c>
+      <c r="D101" t="s">
+        <v>114</v>
+      </c>
+      <c r="E101" t="s">
         <v>61</v>
-      </c>
-      <c r="B101">
-        <v>8</v>
-      </c>
-      <c r="C101">
-        <v>4</v>
-      </c>
-      <c r="D101" t="s">
-        <v>116</v>
-      </c>
-      <c r="E101" t="s">
-        <v>62</v>
       </c>
       <c r="F101" t="b">
         <v>0</v>
@@ -3157,7 +3162,7 @@
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B102">
         <v>8</v>
@@ -3166,21 +3171,21 @@
         <v>4</v>
       </c>
       <c r="D102" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E102" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F102" t="b">
         <v>0</v>
       </c>
       <c r="H102" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B103">
         <v>8</v>
@@ -3189,7 +3194,7 @@
         <v>4</v>
       </c>
       <c r="D103" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F103" t="b">
         <v>0</v>
@@ -3200,7 +3205,7 @@
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B104">
         <v>8</v>
@@ -3209,7 +3214,7 @@
         <v>4</v>
       </c>
       <c r="D104" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F104" t="b">
         <v>0</v>
@@ -3220,7 +3225,7 @@
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B105">
         <v>8</v>
@@ -3229,7 +3234,7 @@
         <v>4</v>
       </c>
       <c r="D105" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F105" t="b">
         <v>0</v>
@@ -3240,536 +3245,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CD6BA00-9BA2-7844-A64E-A182DF7CF650}">
-  <dimension ref="B2:B105"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B10">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B11">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B12">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B13">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B14">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B15">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B16">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B17">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B38">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="39" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B39">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="40" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B40">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="41" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B41">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="42" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B42">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="43" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B43">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="44" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B44">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="45" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B45">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="46" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B46">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B47">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B48">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B49">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B50">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B51">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B52">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B53">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B54">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B55">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B56">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B57">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B58">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B59">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B60">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B61">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B62">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="63" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B63">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="64" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B64">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="65" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B65">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="66" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B66">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="67" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B67">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="68" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B68">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="69" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B69">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="70" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B70">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B71">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B72">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B73">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B74">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="75" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B75">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B76">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B77">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B78">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="79" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B79">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B80">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="81" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B81">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B82">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B83">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="84" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B84">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="85" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B85">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B86">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="87" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B87">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="88" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B88">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="89" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B89">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="90" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B90">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="91" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B91">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="92" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B92">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="93" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B93">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="94" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B94">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="95" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B95">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="96" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B96">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="97" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B97">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="98" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B98">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="99" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B99">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="100" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B100">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="101" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B101">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="102" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B102">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="103" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B103">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="104" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B104">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="105" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B105">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 

--- a/excel/butterScaler/butterScaler23-Section06.xlsx
+++ b/excel/butterScaler/butterScaler23-Section06.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10331"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10407"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shimin/Desktop/Shimin/4-Hobby/Hileft/CreatingMoviesUsingMusicAndScripts/excel/butterScaler/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E883FE1-C07F-244F-82F7-6B97125A9F48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{243058FD-70F4-C24A-BB3C-0B5A0385DC2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="820" yWindow="-22560" windowWidth="30240" windowHeight="18120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="145">
   <si>
     <t>ActionName</t>
   </si>
@@ -449,6 +449,12 @@
   </si>
   <si>
     <t>先做深蹲,  弓步蹲从左脚开始</t>
+  </si>
+  <si>
+    <t>4次半程深蹲</t>
+  </si>
+  <si>
+    <t>4次弓步蹲</t>
   </si>
 </sst>
 </file>
@@ -467,6 +473,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1040,7 +1047,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>143</v>
       </c>
       <c r="B10">
         <v>8</v>
@@ -1063,7 +1070,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>144</v>
       </c>
       <c r="B11">
         <v>8</v>
@@ -1086,7 +1093,7 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>143</v>
       </c>
       <c r="B12">
         <v>8</v>
@@ -1109,7 +1116,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>22</v>
+        <v>144</v>
       </c>
       <c r="B13">
         <v>8</v>
@@ -1132,7 +1139,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>143</v>
       </c>
       <c r="B14">
         <v>8</v>
@@ -1155,7 +1162,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>22</v>
+        <v>144</v>
       </c>
       <c r="B15">
         <v>8</v>
@@ -1178,7 +1185,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>22</v>
+        <v>143</v>
       </c>
       <c r="B16">
         <v>8</v>
@@ -1201,7 +1208,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>22</v>
+        <v>144</v>
       </c>
       <c r="B17">
         <v>8</v>
@@ -2242,7 +2249,7 @@
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>22</v>
+        <v>143</v>
       </c>
       <c r="B62">
         <v>8</v>
@@ -2265,7 +2272,7 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>22</v>
+        <v>144</v>
       </c>
       <c r="B63">
         <v>8</v>
@@ -2288,7 +2295,7 @@
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>22</v>
+        <v>143</v>
       </c>
       <c r="B64">
         <v>8</v>
@@ -2311,7 +2318,7 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>22</v>
+        <v>144</v>
       </c>
       <c r="B65">
         <v>8</v>
@@ -2334,7 +2341,7 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>22</v>
+        <v>143</v>
       </c>
       <c r="B66">
         <v>8</v>
@@ -2357,7 +2364,7 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>22</v>
+        <v>144</v>
       </c>
       <c r="B67">
         <v>8</v>
@@ -2377,7 +2384,7 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>22</v>
+        <v>143</v>
       </c>
       <c r="B68">
         <v>8</v>
@@ -2400,7 +2407,7 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>22</v>
+        <v>144</v>
       </c>
       <c r="B69">
         <v>8</v>

--- a/excel/butterScaler/butterScaler23-Section06.xlsx
+++ b/excel/butterScaler/butterScaler23-Section06.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shimin/Desktop/Shimin/4-Hobby/Hileft/CreatingMoviesUsingMusicAndScripts/excel/butterScaler/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85F3564F-6923-5C43-8C1F-F2A3577E0BF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32862386-D0D6-2D45-8034-AE88D5AECC50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-8700" yWindow="-26160" windowWidth="30240" windowHeight="18120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="131">
   <si>
     <t>ActionName</t>
   </si>
@@ -310,9 +310,6 @@
     <t>4次半程深蹲</t>
   </si>
   <si>
-    <t>4次弓步蹲</t>
-  </si>
-  <si>
     <t>StepActionName</t>
   </si>
   <si>
@@ -398,6 +395,24 @@
   </si>
   <si>
     <t>左腿弓步蹲，也是4个</t>
+  </si>
+  <si>
+    <t>右腿4次弓步蹲</t>
+  </si>
+  <si>
+    <t>左腿4次弓步蹲</t>
+  </si>
+  <si>
+    <t>2次半程深蹲+右腿弓步蹲</t>
+  </si>
+  <si>
+    <t>2次半程深蹲+左腿弓步蹲</t>
+  </si>
+  <si>
+    <t>单次深蹲+右腿弓步蹲</t>
+  </si>
+  <si>
+    <t>单次深蹲+左腿弓步蹲</t>
   </si>
 </sst>
 </file>
@@ -765,7 +780,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.83203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="23.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="35.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8.6640625" bestFit="1" customWidth="1"/>
@@ -781,7 +796,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -897,7 +912,7 @@
         <v>15</v>
       </c>
       <c r="F5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G5" t="b">
         <v>1</v>
@@ -917,7 +932,7 @@
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>129</v>
       </c>
       <c r="D6">
         <v>4</v>
@@ -943,7 +958,7 @@
         <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>16</v>
+        <v>130</v>
       </c>
       <c r="D7">
         <v>4</v>
@@ -969,7 +984,7 @@
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>16</v>
+        <v>129</v>
       </c>
       <c r="D8">
         <v>4</v>
@@ -995,7 +1010,7 @@
         <v>4</v>
       </c>
       <c r="C9" t="s">
-        <v>16</v>
+        <v>130</v>
       </c>
       <c r="D9">
         <v>4</v>
@@ -1047,7 +1062,7 @@
         <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>96</v>
+        <v>125</v>
       </c>
       <c r="D11">
         <v>4</v>
@@ -1056,7 +1071,7 @@
         <v>4321</v>
       </c>
       <c r="F11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G11" t="b">
         <v>0</v>
@@ -1099,13 +1114,13 @@
         <v>8</v>
       </c>
       <c r="C13" t="s">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="D13">
         <v>4</v>
       </c>
       <c r="E13" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F13" t="s">
         <v>25</v>
@@ -1151,7 +1166,7 @@
         <v>8</v>
       </c>
       <c r="C15" t="s">
-        <v>96</v>
+        <v>125</v>
       </c>
       <c r="D15">
         <v>4</v>
@@ -1183,10 +1198,10 @@
         <v>4</v>
       </c>
       <c r="E16" t="s">
+        <v>99</v>
+      </c>
+      <c r="F16" t="s">
         <v>100</v>
-      </c>
-      <c r="F16" t="s">
-        <v>101</v>
       </c>
       <c r="G16" t="b">
         <v>0</v>
@@ -1203,16 +1218,16 @@
         <v>8</v>
       </c>
       <c r="C17" t="s">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="D17">
         <v>4</v>
       </c>
       <c r="E17" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F17" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G17" t="b">
         <v>1</v>
@@ -1232,7 +1247,7 @@
         <v>4</v>
       </c>
       <c r="C18" t="s">
-        <v>28</v>
+        <v>127</v>
       </c>
       <c r="D18">
         <v>4</v>
@@ -1241,7 +1256,7 @@
         <v>1212</v>
       </c>
       <c r="F18" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G18" t="b">
         <v>0</v>
@@ -1258,7 +1273,7 @@
         <v>4</v>
       </c>
       <c r="C19" t="s">
-        <v>28</v>
+        <v>128</v>
       </c>
       <c r="D19">
         <v>4</v>
@@ -1267,7 +1282,7 @@
         <v>67</v>
       </c>
       <c r="F19" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G19" t="b">
         <v>0</v>
@@ -1284,7 +1299,7 @@
         <v>4</v>
       </c>
       <c r="C20" t="s">
-        <v>28</v>
+        <v>127</v>
       </c>
       <c r="D20">
         <v>4</v>
@@ -1310,7 +1325,7 @@
         <v>4</v>
       </c>
       <c r="C21" t="s">
-        <v>28</v>
+        <v>128</v>
       </c>
       <c r="D21">
         <v>4</v>
@@ -1319,7 +1334,7 @@
         <v>69</v>
       </c>
       <c r="F21" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G21" t="b">
         <v>1</v>
@@ -1697,10 +1712,10 @@
         <v>4</v>
       </c>
       <c r="E36" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F36" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G36" t="b">
         <v>0</v>
@@ -1752,7 +1767,7 @@
         <v>4321</v>
       </c>
       <c r="F38" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G38" t="b">
         <v>0</v>
@@ -1769,7 +1784,7 @@
         <v>8</v>
       </c>
       <c r="C39" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D39">
         <v>4</v>
@@ -1778,7 +1793,7 @@
         <v>4321</v>
       </c>
       <c r="F39" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G39" t="b">
         <v>0</v>
@@ -1801,7 +1816,7 @@
         <v>4</v>
       </c>
       <c r="E40" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F40" t="s">
         <v>78</v>
@@ -1821,7 +1836,7 @@
         <v>8</v>
       </c>
       <c r="C41" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D41">
         <v>4</v>
@@ -1873,7 +1888,7 @@
         <v>8</v>
       </c>
       <c r="C43" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D43">
         <v>4</v>
@@ -1919,7 +1934,7 @@
         <v>8</v>
       </c>
       <c r="C45" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D45">
         <v>4</v>
@@ -1928,7 +1943,7 @@
         <v>51</v>
       </c>
       <c r="F45" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G45" t="b">
         <v>1</v>
@@ -1954,7 +1969,7 @@
         <v>4</v>
       </c>
       <c r="E46" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F46" t="s">
         <v>62</v>
@@ -1974,16 +1989,16 @@
         <v>8</v>
       </c>
       <c r="C47" t="s">
+        <v>114</v>
+      </c>
+      <c r="D47">
+        <v>4</v>
+      </c>
+      <c r="E47" t="s">
         <v>115</v>
       </c>
-      <c r="D47">
-        <v>4</v>
-      </c>
-      <c r="E47" t="s">
-        <v>116</v>
-      </c>
       <c r="F47" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G47" t="b">
         <v>0</v>
@@ -2006,10 +2021,10 @@
         <v>4</v>
       </c>
       <c r="E48" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F48" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G48" t="b">
         <v>0</v>
@@ -2026,13 +2041,13 @@
         <v>8</v>
       </c>
       <c r="C49" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D49">
         <v>4</v>
       </c>
       <c r="E49" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F49" t="s">
         <v>52</v>
@@ -2075,7 +2090,7 @@
         <v>8</v>
       </c>
       <c r="C51" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D51">
         <v>4</v>
@@ -2104,7 +2119,7 @@
         <v>4</v>
       </c>
       <c r="E52" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G52" t="b">
         <v>0</v>
@@ -2121,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="C53" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D53">
         <v>4</v>
       </c>
       <c r="E53" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G53" t="b">
         <v>1</v>
@@ -2254,7 +2269,7 @@
         <v>4</v>
       </c>
       <c r="C58" t="s">
-        <v>16</v>
+        <v>130</v>
       </c>
       <c r="D58">
         <v>4</v>
@@ -2280,7 +2295,7 @@
         <v>4</v>
       </c>
       <c r="C59" t="s">
-        <v>16</v>
+        <v>129</v>
       </c>
       <c r="D59">
         <v>4</v>
@@ -2306,7 +2321,7 @@
         <v>4</v>
       </c>
       <c r="C60" t="s">
-        <v>16</v>
+        <v>130</v>
       </c>
       <c r="D60">
         <v>4</v>
@@ -2332,7 +2347,7 @@
         <v>4</v>
       </c>
       <c r="C61" t="s">
-        <v>16</v>
+        <v>129</v>
       </c>
       <c r="D61">
         <v>4</v>
@@ -2384,7 +2399,7 @@
         <v>8</v>
       </c>
       <c r="C63" t="s">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="D63">
         <v>4</v>
@@ -2393,7 +2408,7 @@
         <v>4321</v>
       </c>
       <c r="F63" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G63" t="b">
         <v>0</v>
@@ -2436,13 +2451,13 @@
         <v>8</v>
       </c>
       <c r="C65" t="s">
-        <v>96</v>
+        <v>125</v>
       </c>
       <c r="D65">
         <v>4</v>
       </c>
       <c r="E65" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F65" t="s">
         <v>25</v>
@@ -2488,7 +2503,7 @@
         <v>8</v>
       </c>
       <c r="C67" t="s">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="D67">
         <v>4</v>
@@ -2520,10 +2535,10 @@
         <v>4</v>
       </c>
       <c r="E68" t="s">
+        <v>99</v>
+      </c>
+      <c r="F68" t="s">
         <v>100</v>
-      </c>
-      <c r="F68" t="s">
-        <v>101</v>
       </c>
       <c r="G68" t="b">
         <v>0</v>
@@ -2540,16 +2555,16 @@
         <v>8</v>
       </c>
       <c r="C69" t="s">
-        <v>96</v>
+        <v>125</v>
       </c>
       <c r="D69">
         <v>4</v>
       </c>
       <c r="E69" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F69" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G69" t="b">
         <v>1</v>
@@ -2569,7 +2584,7 @@
         <v>4</v>
       </c>
       <c r="C70" t="s">
-        <v>28</v>
+        <v>128</v>
       </c>
       <c r="D70">
         <v>4</v>
@@ -2578,7 +2593,7 @@
         <v>1212</v>
       </c>
       <c r="F70" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G70" t="b">
         <v>0</v>
@@ -2595,7 +2610,7 @@
         <v>4</v>
       </c>
       <c r="C71" t="s">
-        <v>28</v>
+        <v>127</v>
       </c>
       <c r="D71">
         <v>4</v>
@@ -2621,7 +2636,7 @@
         <v>4</v>
       </c>
       <c r="C72" t="s">
-        <v>28</v>
+        <v>128</v>
       </c>
       <c r="D72">
         <v>4</v>
@@ -2647,7 +2662,7 @@
         <v>4</v>
       </c>
       <c r="C73" t="s">
-        <v>28</v>
+        <v>127</v>
       </c>
       <c r="D73">
         <v>4</v>
@@ -3098,7 +3113,7 @@
         <v>4321</v>
       </c>
       <c r="F90" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G90" t="b">
         <v>0</v>
@@ -3115,7 +3130,7 @@
         <v>8</v>
       </c>
       <c r="C91" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D91">
         <v>4</v>
@@ -3124,7 +3139,7 @@
         <v>4321</v>
       </c>
       <c r="F91" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G91" t="b">
         <v>0</v>
@@ -3147,7 +3162,7 @@
         <v>4</v>
       </c>
       <c r="E92" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F92" t="s">
         <v>78</v>
@@ -3167,7 +3182,7 @@
         <v>8</v>
       </c>
       <c r="C93" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D93">
         <v>4</v>
@@ -3219,7 +3234,7 @@
         <v>8</v>
       </c>
       <c r="C95" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D95">
         <v>4</v>
@@ -3265,7 +3280,7 @@
         <v>8</v>
       </c>
       <c r="C97" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D97">
         <v>4</v>
@@ -3274,7 +3289,7 @@
         <v>51</v>
       </c>
       <c r="F97" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G97" t="b">
         <v>1</v>
@@ -3300,7 +3315,7 @@
         <v>4</v>
       </c>
       <c r="E98" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F98" t="s">
         <v>62</v>
@@ -3320,16 +3335,16 @@
         <v>8</v>
       </c>
       <c r="C99" t="s">
+        <v>114</v>
+      </c>
+      <c r="D99">
+        <v>4</v>
+      </c>
+      <c r="E99" t="s">
         <v>115</v>
       </c>
-      <c r="D99">
-        <v>4</v>
-      </c>
-      <c r="E99" t="s">
-        <v>116</v>
-      </c>
       <c r="F99" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G99" t="b">
         <v>0</v>
@@ -3352,10 +3367,10 @@
         <v>4</v>
       </c>
       <c r="E100" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F100" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G100" t="b">
         <v>0</v>
@@ -3372,13 +3387,13 @@
         <v>8</v>
       </c>
       <c r="C101" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D101">
         <v>4</v>
       </c>
       <c r="E101" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F101" t="s">
         <v>52</v>
@@ -3421,7 +3436,7 @@
         <v>8</v>
       </c>
       <c r="C103" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D103">
         <v>4</v>
@@ -3450,7 +3465,7 @@
         <v>4</v>
       </c>
       <c r="E104" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G104" t="b">
         <v>0</v>
@@ -3467,13 +3482,13 @@
         <v>8</v>
       </c>
       <c r="C105" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D105">
         <v>4</v>
       </c>
       <c r="E105" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G105" t="b">
         <v>0</v>
